--- a/job_description.xlsx
+++ b/job_description.xlsx
@@ -37,22 +37,22 @@
     <t>Company_name</t>
   </si>
   <si>
-    <t>Data Scientist</t>
-  </si>
-  <si>
-    <t>Bachelor's or Master’s degree in Data Science, or a field with a strong quantitative and analytic focus such as Computer Science, Engineering, Mathematics, Statistics, Economics, Operations Research, or other related field.</t>
+    <t>Data Scientist I</t>
+  </si>
+  <si>
+    <t>Bachelor's degree or equivalent years of experience and/or certification in Data Science, Computer Science, Statistics, Mathematics or Engineering</t>
   </si>
   <si>
     <t>Chennai, Tamil Nadu, India</t>
   </si>
   <si>
-    <t>Algorithms, Applied Mathematics, Computer Science, Python (Programming Language), Machine Learning, Natural Language Processing (NLP), SciPy, SQL (Programming Language), Statistics, Data Science, Data visualization, Large Data Set Processing, Solid Programming capabilities in Python, SQL, Statistical or Machine Learning Methods</t>
+    <t>Python, Pandas, NumPy, scikit-learn, SQL, TensorFlow, Keras, Torch, Caffe, Hadoop, Spark</t>
   </si>
   <si>
     <t>Full-time</t>
   </si>
   <si>
-    <t>Lightcast</t>
+    <t>Cambridge Mobile Telematics</t>
   </si>
 </sst>
 </file>

--- a/job_description.xlsx
+++ b/job_description.xlsx
@@ -37,22 +37,22 @@
     <t>Company_name</t>
   </si>
   <si>
-    <t>Data Scientist I</t>
-  </si>
-  <si>
-    <t>Bachelor's degree or equivalent years of experience and/or certification in Data Science, Computer Science, Statistics, Mathematics or Engineering</t>
-  </si>
-  <si>
-    <t>Chennai, Tamil Nadu, India</t>
-  </si>
-  <si>
-    <t>Python, Pandas, NumPy, scikit-learn, SQL, TensorFlow, Keras, Torch, Caffe, Hadoop, Spark</t>
+    <t>Machine Learning Intern</t>
+  </si>
+  <si>
+    <t>Currently pursuing or completed a degree in Computer Science, Mathematics, Statistics, or related field</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Computer Science and Algorithms skills, Deep Learning and Machine Learning skills, Statistics knowledge, Understanding of neural networks and ensembles, Strong problem-solving skills, Ability to work collaboratively in a team environment, Experience with Python, TensorFlow, or other relevant tools</t>
   </si>
   <si>
     <t>Full-time</t>
   </si>
   <si>
-    <t>Cambridge Mobile Telematics</t>
+    <t>Shodh AI</t>
   </si>
 </sst>
 </file>
@@ -447,7 +447,7 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>

--- a/job_description.xlsx
+++ b/job_description.xlsx
@@ -37,22 +37,22 @@
     <t>Company_name</t>
   </si>
   <si>
-    <t>Machine Learning Intern</t>
-  </si>
-  <si>
-    <t>Currently pursuing or completed a degree in Computer Science, Mathematics, Statistics, or related field</t>
+    <t>Data Science &amp; Engineering Intern</t>
+  </si>
+  <si>
+    <t>Graduate (UG / PG) in Sales and Marketing or Retail management. or Engineering. MBA in Sales and Marketing would be an advantage</t>
   </si>
   <si>
     <t>India</t>
   </si>
   <si>
-    <t>Computer Science and Algorithms skills, Deep Learning and Machine Learning skills, Statistics knowledge, Understanding of neural networks and ensembles, Strong problem-solving skills, Ability to work collaboratively in a team environment, Experience with Python, TensorFlow, or other relevant tools</t>
-  </si>
-  <si>
-    <t>Full-time</t>
-  </si>
-  <si>
-    <t>Shodh AI</t>
+    <t>Python (pandas, NumPy, scikit-learn, etc.), Data engineering and pipeline design, Data cleaning and preprocessing, ML modeling (supervised and unsupervised techniques), Data visualization (Matplotlib, Seaborn, Plotly, or similar), Fluent English Communication Skills (Oral, Written &amp; Presentation), Excellent Spoken &amp; written communication skills in English, and any 1 local language, Good Understanding about Lead Research, Lead Gathering, sales Forecasting in Software, SaaS, Internet or Application based companies</t>
+  </si>
+  <si>
+    <t>Internship</t>
+  </si>
+  <si>
+    <t>Razonica</t>
   </si>
 </sst>
 </file>
@@ -447,7 +447,7 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>

--- a/job_description.xlsx
+++ b/job_description.xlsx
@@ -37,22 +37,22 @@
     <t>Company_name</t>
   </si>
   <si>
-    <t>Data Science &amp; Engineering Intern</t>
-  </si>
-  <si>
-    <t>Graduate (UG / PG) in Sales and Marketing or Retail management. or Engineering. MBA in Sales and Marketing would be an advantage</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Python (pandas, NumPy, scikit-learn, etc.), Data engineering and pipeline design, Data cleaning and preprocessing, ML modeling (supervised and unsupervised techniques), Data visualization (Matplotlib, Seaborn, Plotly, or similar), Fluent English Communication Skills (Oral, Written &amp; Presentation), Excellent Spoken &amp; written communication skills in English, and any 1 local language, Good Understanding about Lead Research, Lead Gathering, sales Forecasting in Software, SaaS, Internet or Application based companies</t>
-  </si>
-  <si>
-    <t>Internship</t>
-  </si>
-  <si>
-    <t>Razonica</t>
+    <t>AI/ML Engineer</t>
+  </si>
+  <si>
+    <t>Bachelor's or Master's degree in Computer Science, Artificial Intelligence, Machine Learning, Data Science, or a closely related quantitative field.</t>
+  </si>
+  <si>
+    <t>Bengaluru, Karnataka, India</t>
+  </si>
+  <si>
+    <t>Python, Pandas, NumPy, Scikit-learn, TensorFlow, PyTorch, Keras, NLP, Computer Vision</t>
+  </si>
+  <si>
+    <t>Full-time</t>
+  </si>
+  <si>
+    <t>Abstrabit Technologies</t>
   </si>
 </sst>
 </file>
@@ -447,7 +447,7 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>

--- a/job_description.xlsx
+++ b/job_description.xlsx
@@ -37,22 +37,22 @@
     <t>Company_name</t>
   </si>
   <si>
-    <t>AI/ML Engineer</t>
-  </si>
-  <si>
-    <t>Bachelor's or Master's degree in Computer Science, Artificial Intelligence, Machine Learning, Data Science, or a closely related quantitative field.</t>
+    <t>Machine Learning Engineer (Multiple)</t>
+  </si>
+  <si>
+    <t>Master’s degree or Ph.D. in Computer Science, Machine Learning, or a related quantitative field</t>
   </si>
   <si>
     <t>Bengaluru, Karnataka, India</t>
   </si>
   <si>
-    <t>Python, Pandas, NumPy, Scikit-learn, TensorFlow, PyTorch, Keras, NLP, Computer Vision</t>
+    <t>Python, TensorFlow, PyTorch, SQL, ETL, data warehousing, NLP techniques and frameworks, retrieval, ranking, reinforcement learning, and agent-based systems, MLOps principles and best practices, cloud platforms like GCP or Azure, latest industry and academic trends in machine learning and AI</t>
   </si>
   <si>
     <t>Full-time</t>
   </si>
   <si>
-    <t>Abstrabit Technologies</t>
+    <t>Ema Unlimited</t>
   </si>
 </sst>
 </file>

--- a/job_description.xlsx
+++ b/job_description.xlsx
@@ -37,22 +37,22 @@
     <t>Company_name</t>
   </si>
   <si>
-    <t>Machine Learning Engineer (Multiple)</t>
-  </si>
-  <si>
-    <t>Master’s degree or Ph.D. in Computer Science, Machine Learning, or a related quantitative field</t>
+    <t>Internship AI</t>
+  </si>
+  <si>
+    <t>Engg. background with exposure to Machine Learning &amp; Deep Learning, Artificial Intelligence</t>
   </si>
   <si>
     <t>Bengaluru, Karnataka, India</t>
   </si>
   <si>
-    <t>Python, TensorFlow, PyTorch, SQL, ETL, data warehousing, NLP techniques and frameworks, retrieval, ranking, reinforcement learning, and agent-based systems, MLOps principles and best practices, cloud platforms like GCP or Azure, latest industry and academic trends in machine learning and AI</t>
-  </si>
-  <si>
-    <t>Full-time</t>
-  </si>
-  <si>
-    <t>Ema Unlimited</t>
+    <t>Python, Machine Learning Frameworks like Tensorflow/PyTorch, Network Graph Visualization techniques, Compressible Flow Aerodynamics</t>
+  </si>
+  <si>
+    <t>Internship</t>
+  </si>
+  <si>
+    <t>Airbus</t>
   </si>
 </sst>
 </file>

--- a/job_description.xlsx
+++ b/job_description.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>job_title</t>
   </si>
@@ -37,22 +37,19 @@
     <t>Company_name</t>
   </si>
   <si>
-    <t>Internship AI</t>
-  </si>
-  <si>
-    <t>Engg. background with exposure to Machine Learning &amp; Deep Learning, Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>Bengaluru, Karnataka, India</t>
-  </si>
-  <si>
-    <t>Python, Machine Learning Frameworks like Tensorflow/PyTorch, Network Graph Visualization techniques, Compressible Flow Aerodynamics</t>
+    <t>Data Science Internship in Chennai</t>
+  </si>
+  <si>
+    <t>Chennai, Tamil Nadu, India</t>
+  </si>
+  <si>
+    <t>Artificial intelligence, Python, SQL, Data Analytics, Machine Learning, Data Science, Natural Language Processing (NLP), Deep Learning</t>
   </si>
   <si>
     <t>Internship</t>
   </si>
   <si>
-    <t>Airbus</t>
+    <t>Approlabs</t>
   </si>
 </sst>
 </file>
@@ -440,23 +437,20 @@
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
